--- a/data/trans_camb/P1402-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P1402-Clase-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3,83</t>
+          <t>3,92</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,3</t>
+          <t>1,35</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>2,4</t>
+          <t>2,47</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,95; 1,48</t>
+          <t>-4,4; 1,33</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,94; 6,08</t>
+          <t>-0,99; 5,68</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,77; 7,3</t>
+          <t>1,01; 7,11</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,08; 4,29</t>
+          <t>-1,1; 4,3</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,37; 6,26</t>
+          <t>-0,06; 5,25</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-0,81; 3,16</t>
+          <t>-0,72; 3,17</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-2,11; 1,85</t>
+          <t>-2,07; 2,03</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,19; 4,44</t>
+          <t>0,12; 4,7</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,47; 4,39</t>
+          <t>0,41; 4,23</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>74,48%</t>
+          <t>76,17%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>67,27%</t>
+          <t>70,14%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>61,75%</t>
+          <t>63,55%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-58,6; 46,3</t>
+          <t>-62,16; 34,96</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-18,98; 157,28</t>
+          <t>-19,55; 143,05</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12,67; 219,5</t>
+          <t>13,08; 194,34</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-51,66; 432,32</t>
+          <t>-49,51; 402,74</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-8,51; 638,44</t>
+          <t>-11,46; 614,25</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-26,89; 393,95</t>
+          <t>-24,6; 411,82</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-42,94; 65,33</t>
+          <t>-45,39; 71,4</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,16; 151,1</t>
+          <t>-0,81; 166,49</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>8,35; 156,66</t>
+          <t>7,86; 148,95</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>4,27</t>
+          <t>3,82</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,14</t>
+          <t>0,16</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2,49</t>
+          <t>2,21</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,89; 3,71</t>
+          <t>-2,52; 3,83</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,07; 5,79</t>
+          <t>-0,86; 5,77</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,88; 7,36</t>
+          <t>0,74; 6,96</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,0; 3,19</t>
+          <t>-1,76; 3,27</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,85; 3,28</t>
+          <t>-1,96; 3,27</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-2,37; 1,83</t>
+          <t>-2,29; 2,0</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-1,1; 2,67</t>
+          <t>-1,14; 2,76</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-0,38; 3,87</t>
+          <t>-0,38; 3,79</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,49; 4,52</t>
+          <t>0,35; 4,12</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>88,48%</t>
+          <t>79,21%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>70,58%</t>
+          <t>62,49%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-41,15; 109,19</t>
+          <t>-42,24; 115,18</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-19,2; 186,84</t>
+          <t>-19,84; 164,35</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8,77; 215,93</t>
+          <t>10,34; 210,52</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-64,36; 288,34</t>
+          <t>-58,59; 273,7</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-61,25; 295,49</t>
+          <t>-61,26; 268,82</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-63,9; 185,74</t>
+          <t>-60,35; 196,0</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-26,24; 111,73</t>
+          <t>-29,05; 100,95</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-10,12; 154,46</t>
+          <t>-9,39; 140,96</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>9,18; 184,74</t>
+          <t>3,96; 162,63</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2,62</t>
+          <t>6,4</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,07</t>
+          <t>1,92</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2,4</t>
+          <t>5,27</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,33; 9,55</t>
+          <t>3,38; 9,59</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,15; 8,66</t>
+          <t>2,16; 8,36</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,35; 8,09</t>
+          <t>3,46; 9,68</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-7,79; 2,99</t>
+          <t>-7,39; 2,82</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-7,94; 3,31</t>
+          <t>-7,89; 3,69</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-3,86; 6,67</t>
+          <t>-3,9; 7,18</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,55; 7,01</t>
+          <t>1,49; 7,04</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,63; 6,07</t>
+          <t>0,97; 6,55</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-3,38; 6,56</t>
+          <t>2,49; 7,92</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>51,71%</t>
+          <t>126,45%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>25,55%</t>
+          <t>23,76%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>41,52%</t>
+          <t>91,27%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>48,38; 258,14</t>
+          <t>47,95; 240,36</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>32,42; 228,97</t>
+          <t>31,56; 210,28</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-49,83; 179,6</t>
+          <t>54,06; 259,9</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-65,54; 63,36</t>
+          <t>-63,19; 54,86</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-73,86; 67,42</t>
+          <t>-73,82; 77,23</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-33,08; 130,08</t>
+          <t>-36,74; 143,85</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>21,55; 154,62</t>
+          <t>22,18; 154,23</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>8,06; 129,61</t>
+          <t>11,38; 145,18</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-46,94; 120,91</t>
+          <t>33,49; 173,46</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3,61</t>
+          <t>3,94</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,13</t>
+          <t>1,37</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>1,56</t>
+          <t>2,63</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,87; 3,53</t>
+          <t>-0,85; 3,69</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,04; 4,51</t>
+          <t>0,09; 4,64</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,24; 5,69</t>
+          <t>1,66; 6,19</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,38; 3,16</t>
+          <t>-1,15; 3,46</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,71; 1,46</t>
+          <t>-2,79; 1,43</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-3,08; 2,34</t>
+          <t>-0,7; 3,24</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,72; 2,71</t>
+          <t>-0,47; 2,8</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 2,38</t>
+          <t>-0,83; 2,51</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-0,96; 3,25</t>
+          <t>1,1; 4,31</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>47,75%</t>
+          <t>52,13%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>29,8%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>24,09%</t>
+          <t>40,64%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-11,02; 52,27</t>
+          <t>-9,81; 55,89</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-0,34; 69,27</t>
+          <t>0,35; 70,41</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>13,31; 87,37</t>
+          <t>19,61; 93,98</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-23,86; 88,99</t>
+          <t>-20,4; 95,78</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-46,93; 45,79</t>
+          <t>-48,7; 42,8</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-48,33; 60,03</t>
+          <t>-12,5; 96,01</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-10,15; 46,69</t>
+          <t>-6,48; 48,31</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-8,92; 41,26</t>
+          <t>-11,39; 42,95</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-14,34; 54,17</t>
+          <t>14,92; 74,7</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2,74</t>
+          <t>2,17</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>4,13</t>
+          <t>5,33</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>3,62</t>
+          <t>4,05</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-2,74; 4,14</t>
+          <t>-3,19; 3,97</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,29; 8,01</t>
+          <t>0,65; 7,93</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-1,11; 6,03</t>
+          <t>-1,37; 5,39</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,53; 6,23</t>
+          <t>0,24; 6,53</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,75; 6,61</t>
+          <t>0,54; 6,6</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,06; 7,14</t>
+          <t>2,57; 8,06</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,25; 4,65</t>
+          <t>0,06; 4,48</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1,95; 6,48</t>
+          <t>1,75; 6,43</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1,03; 5,84</t>
+          <t>1,9; 5,9</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>43,04%</t>
+          <t>34,01%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>66,96%</t>
+          <t>86,44%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>58,05%</t>
+          <t>64,91%</t>
         </is>
       </c>
     </row>
@@ -1647,54 +1647,54 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-34,38; 91,72</t>
+          <t>-39,08; 88,56</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>1,07; 171,25</t>
+          <t>5,81; 183,18</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-13,86; 132,57</t>
+          <t>-17,6; 123,42</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>6,7; 136,84</t>
+          <t>1,57; 138,69</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>8,68; 140,24</t>
+          <t>5,55; 139,35</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>15,48; 150,91</t>
+          <t>32,55; 176,05</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>3,21; 92,69</t>
+          <t>0,79; 88,14</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>25,5; 122,23</t>
+          <t>22,82; 129,0</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>12,39; 111,78</t>
+          <t>24,81; 114,55</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0,84</t>
+          <t>0,85</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0,88</t>
+          <t>0,71</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>0,36</t>
+          <t>0,45</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>0,71; 5,0</t>
+          <t>0,74; 5,01</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>0,4; 3,75</t>
+          <t>0,39; 3,27</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>0,2; 2,53</t>
+          <t>0,23; 2,53</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>0,68; 5,99</t>
+          <t>0,99; 6,08</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>0,67; 6,7</t>
+          <t>0,47; 6,36</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-1,44; 3,43</t>
+          <t>-2,01; 3,06</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>0,72; 5,47</t>
+          <t>0,58; 5,46</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>0,86; 5,49</t>
+          <t>0,67; 5,3</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-1,67; 2,27</t>
+          <t>-1,67; 2,5</t>
         </is>
       </c>
     </row>
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>5,25%</t>
         </is>
       </c>
     </row>
@@ -1878,32 +1878,32 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>5,73; 62,14</t>
+          <t>8,87; 65,06</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>5,07; 69,57</t>
+          <t>3,81; 64,85</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-11,95; 36,87</t>
+          <t>-16,91; 31,94</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>7,03; 69,3</t>
+          <t>6,21; 70,77</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>8,59; 68,98</t>
+          <t>7,52; 71,59</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-17,49; 30,06</t>
+          <t>-17,73; 31,68</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>3,17</t>
+          <t>3,81</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,52</t>
+          <t>1,14</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>1,82</t>
+          <t>2,44</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>0,61; 3,07</t>
+          <t>0,6; 2,97</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>1,68; 4,29</t>
+          <t>1,96; 4,32</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>0,99; 4,61</t>
+          <t>2,71; 5,06</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>0,56; 3,14</t>
+          <t>0,42; 3,08</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>0,32; 3,09</t>
+          <t>0,36; 2,89</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-1,27; 1,68</t>
+          <t>0,07; 2,22</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>1,0; 2,67</t>
+          <t>0,99; 2,74</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>1,48; 3,22</t>
+          <t>1,46; 3,24</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>0,58; 2,76</t>
+          <t>1,65; 3,23</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>55,97%</t>
+          <t>67,16%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>16,79%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>29,1%</t>
+          <t>39,18%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>9,92; 61,69</t>
+          <t>9,05; 58,21</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>25,23; 83,45</t>
+          <t>31,19; 83,34</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>16,23; 86,62</t>
+          <t>41,96; 97,15</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>7,31; 51,74</t>
+          <t>5,85; 49,72</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>4,21; 49,88</t>
+          <t>4,78; 47,81</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-17,3; 26,76</t>
+          <t>0,91; 36,67</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>15,43; 45,85</t>
+          <t>15,33; 47,12</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>22,31; 54,96</t>
+          <t>21,36; 55,66</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>9,41; 45,78</t>
+          <t>23,85; 54,57</t>
         </is>
       </c>
     </row>
